--- a/Data/2018_F013B4_CO_ITR/2018_F013B4_CO_ITR_SoilAnalysis.xlsx
+++ b/Data/2018_F013B4_CO_ITR/2018_F013B4_CO_ITR_SoilAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2018_F013B4_CO_ITR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{693612C9-5182-4CA7-90EB-3187D4BC15F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E5B527D-9E0C-4CC2-AD2A-67C0FEB17FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16320" yWindow="-28050" windowWidth="17910" windowHeight="25080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1665" yWindow="-26850" windowWidth="27270" windowHeight="17295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDJH" sheetId="5" r:id="rId1"/>
@@ -812,9 +812,6 @@
     <t>p01-1</t>
   </si>
   <si>
-    <t>2013d260EM38</t>
-  </si>
-  <si>
     <t>2015d118EM38</t>
   </si>
   <si>
@@ -1458,6 +1455,9 @@
   </si>
   <si>
     <t>2016-p04-1</t>
+  </si>
+  <si>
+    <t>2013d260EM38V</t>
   </si>
 </sst>
 </file>
@@ -2280,13 +2280,13 @@
         <v>201</v>
       </c>
       <c r="B1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E1" t="s">
         <v>12</v>
@@ -2297,7 +2297,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C2">
         <v>408901.33329999901</v>
@@ -2314,7 +2314,7 @@
         <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C3">
         <v>408900.44150000002</v>
@@ -2331,7 +2331,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C4">
         <v>408899.99949999899</v>
@@ -2348,7 +2348,7 @@
         <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C5">
         <v>408899.580599999</v>
@@ -2365,7 +2365,7 @@
         <v>151</v>
       </c>
       <c r="B6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C6">
         <v>408879.86940000003</v>
@@ -2382,7 +2382,7 @@
         <v>152</v>
       </c>
       <c r="B7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C7">
         <v>408879.400499999</v>
@@ -2399,7 +2399,7 @@
         <v>153</v>
       </c>
       <c r="B8" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C8">
         <v>408878.89939999901</v>
@@ -2416,7 +2416,7 @@
         <v>155</v>
       </c>
       <c r="B9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C9">
         <v>408877.92340000003</v>
@@ -2433,7 +2433,7 @@
         <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C10">
         <v>408872.89059999899</v>
@@ -2450,7 +2450,7 @@
         <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C11">
         <v>408872.00809999899</v>
@@ -2467,7 +2467,7 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C12">
         <v>408871.57900000003</v>
@@ -2484,7 +2484,7 @@
         <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C13">
         <v>408871.13660000003</v>
@@ -2501,7 +2501,7 @@
         <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C14">
         <v>408845.46089999902</v>
@@ -2518,7 +2518,7 @@
         <v>156</v>
       </c>
       <c r="B15" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C15">
         <v>408850.18070000003</v>
@@ -2535,7 +2535,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C16">
         <v>408844.56319999899</v>
@@ -2552,7 +2552,7 @@
         <v>157</v>
       </c>
       <c r="B17" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C17">
         <v>408849.70020000002</v>
@@ -2569,7 +2569,7 @@
         <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C18">
         <v>408844.13500000001</v>
@@ -2586,7 +2586,7 @@
         <v>158</v>
       </c>
       <c r="B19" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C19">
         <v>408849.219199999</v>
@@ -2603,7 +2603,7 @@
         <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C20">
         <v>408843.68329999998</v>
@@ -2620,7 +2620,7 @@
         <v>160</v>
       </c>
       <c r="B21" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C21">
         <v>408848.231299999</v>
@@ -2637,7 +2637,7 @@
         <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C22">
         <v>408817.00829999999</v>
@@ -2654,7 +2654,7 @@
         <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C23">
         <v>408816.12689999898</v>
@@ -2671,7 +2671,7 @@
         <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C24">
         <v>408815.666399999</v>
@@ -2688,7 +2688,7 @@
         <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C25">
         <v>408815.248499999</v>
@@ -2705,7 +2705,7 @@
         <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C26">
         <v>408788.581799999</v>
@@ -2722,7 +2722,7 @@
         <v>166</v>
       </c>
       <c r="B27" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C27">
         <v>408793.35800000001</v>
@@ -2739,7 +2739,7 @@
         <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C28">
         <v>408787.67560000002</v>
@@ -2756,7 +2756,7 @@
         <v>167</v>
       </c>
       <c r="B29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C29">
         <v>408792.866099999</v>
@@ -2773,7 +2773,7 @@
         <v>52</v>
       </c>
       <c r="B30" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C30">
         <v>408787.222799999</v>
@@ -2790,7 +2790,7 @@
         <v>168</v>
       </c>
       <c r="B31" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C31">
         <v>408792.38530000002</v>
@@ -2807,7 +2807,7 @@
         <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C32">
         <v>408786.80749999901</v>
@@ -2824,7 +2824,7 @@
         <v>170</v>
       </c>
       <c r="B33" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C33">
         <v>408791.43050000002</v>
@@ -2841,7 +2841,7 @@
         <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C34">
         <v>408760.11839999899</v>
@@ -2858,7 +2858,7 @@
         <v>58</v>
       </c>
       <c r="B35" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C35">
         <v>408759.24219999899</v>
@@ -2875,7 +2875,7 @@
         <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C36">
         <v>408758.807399999</v>
@@ -2892,7 +2892,7 @@
         <v>56</v>
       </c>
       <c r="B37" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C37">
         <v>408758.367499999</v>
@@ -2909,7 +2909,7 @@
         <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C38">
         <v>408748.9094</v>
@@ -2926,7 +2926,7 @@
         <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C39">
         <v>408748.6594</v>
@@ -2943,7 +2943,7 @@
         <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C40">
         <v>408742.57679999899</v>
@@ -2960,7 +2960,7 @@
         <v>82</v>
       </c>
       <c r="B41" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C41">
         <v>408742.84710000001</v>
@@ -2977,7 +2977,7 @@
         <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C42">
         <v>408748.33390000003</v>
@@ -2994,7 +2994,7 @@
         <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C43">
         <v>408747.98800000001</v>
@@ -3011,7 +3011,7 @@
         <v>79</v>
       </c>
       <c r="B44" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C44">
         <v>408741.9215</v>
@@ -3028,7 +3028,7 @@
         <v>80</v>
       </c>
       <c r="B45" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C45">
         <v>408742.204399999</v>
@@ -3045,7 +3045,7 @@
         <v>71</v>
       </c>
       <c r="B46" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C46">
         <v>408747.652899999</v>
@@ -3062,7 +3062,7 @@
         <v>78</v>
       </c>
       <c r="B47" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C47">
         <v>408741.583099999</v>
@@ -3079,7 +3079,7 @@
         <v>73</v>
       </c>
       <c r="B48" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C48">
         <v>408747.01990000001</v>
@@ -3096,7 +3096,7 @@
         <v>76</v>
       </c>
       <c r="B49" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C49">
         <v>408740.96580000001</v>
@@ -3113,7 +3113,7 @@
         <v>83</v>
       </c>
       <c r="B50" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C50">
         <v>408734.69020000001</v>
@@ -3130,7 +3130,7 @@
         <v>84</v>
       </c>
       <c r="B51" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C51">
         <v>408734.44760000001</v>
@@ -3147,7 +3147,7 @@
         <v>97</v>
       </c>
       <c r="B52" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C52">
         <v>408728.347899999</v>
@@ -3164,7 +3164,7 @@
         <v>98</v>
       </c>
       <c r="B53" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C53">
         <v>408728.57990000001</v>
@@ -3181,7 +3181,7 @@
         <v>85</v>
       </c>
       <c r="B54" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C54">
         <v>408734.16200000001</v>
@@ -3198,7 +3198,7 @@
         <v>86</v>
       </c>
       <c r="B55" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C55">
         <v>408733.81439999898</v>
@@ -3215,7 +3215,7 @@
         <v>95</v>
       </c>
       <c r="B56" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C56">
         <v>408727.74089999998</v>
@@ -3232,7 +3232,7 @@
         <v>96</v>
       </c>
       <c r="B57" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C57">
         <v>408727.98920000001</v>
@@ -3249,7 +3249,7 @@
         <v>87</v>
       </c>
       <c r="B58" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C58">
         <v>408733.443499999</v>
@@ -3266,7 +3266,7 @@
         <v>94</v>
       </c>
       <c r="B59" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C59">
         <v>408727.3763</v>
@@ -3283,7 +3283,7 @@
         <v>89</v>
       </c>
       <c r="B60" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C60">
         <v>408732.84250000003</v>
@@ -3300,7 +3300,7 @@
         <v>92</v>
       </c>
       <c r="B61" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C61">
         <v>408726.75140000001</v>
@@ -3317,7 +3317,7 @@
         <v>99</v>
       </c>
       <c r="B62" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C62">
         <v>408720.46580000001</v>
@@ -3334,7 +3334,7 @@
         <v>100</v>
       </c>
       <c r="B63" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C63">
         <v>408720.19679999899</v>
@@ -3351,7 +3351,7 @@
         <v>113</v>
       </c>
       <c r="B64" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C64">
         <v>408714.09700000001</v>
@@ -3368,7 +3368,7 @@
         <v>114</v>
       </c>
       <c r="B65" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C65">
         <v>408714.40309999901</v>
@@ -3385,7 +3385,7 @@
         <v>101</v>
       </c>
       <c r="B66" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C66">
         <v>408719.8885</v>
@@ -3402,7 +3402,7 @@
         <v>102</v>
       </c>
       <c r="B67" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C67">
         <v>408719.60830000002</v>
@@ -3419,7 +3419,7 @@
         <v>111</v>
       </c>
       <c r="B68" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C68">
         <v>408713.53340000001</v>
@@ -3436,7 +3436,7 @@
         <v>112</v>
       </c>
       <c r="B69" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C69">
         <v>408713.790299999</v>
@@ -3453,7 +3453,7 @@
         <v>103</v>
       </c>
       <c r="B70" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C70">
         <v>408719.22999999899</v>
@@ -3470,7 +3470,7 @@
         <v>110</v>
       </c>
       <c r="B71" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C71">
         <v>408713.13880000002</v>
@@ -3487,7 +3487,7 @@
         <v>105</v>
       </c>
       <c r="B72" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C72">
         <v>408718.61729999899</v>
@@ -3504,7 +3504,7 @@
         <v>108</v>
       </c>
       <c r="B73" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C73">
         <v>408712.455599999</v>
@@ -3521,7 +3521,7 @@
         <v>115</v>
       </c>
       <c r="B74" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C74">
         <v>408706.2476</v>
@@ -3538,7 +3538,7 @@
         <v>116</v>
       </c>
       <c r="B75" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C75">
         <v>408705.94109999901</v>
@@ -3555,7 +3555,7 @@
         <v>129</v>
       </c>
       <c r="B76" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C76">
         <v>408699.85230000003</v>
@@ -3572,7 +3572,7 @@
         <v>130</v>
       </c>
       <c r="B77" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C77">
         <v>408700.13030000002</v>
@@ -3589,7 +3589,7 @@
         <v>117</v>
       </c>
       <c r="B78" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C78">
         <v>408705.62539999897</v>
@@ -3606,7 +3606,7 @@
         <v>118</v>
       </c>
       <c r="B79" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C79">
         <v>408705.38500000001</v>
@@ -3623,7 +3623,7 @@
         <v>127</v>
       </c>
       <c r="B80" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C80">
         <v>408699.26530000003</v>
@@ -3640,7 +3640,7 @@
         <v>128</v>
       </c>
       <c r="B81" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C81">
         <v>408699.535299999</v>
@@ -3657,7 +3657,7 @@
         <v>119</v>
       </c>
       <c r="B82" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C82">
         <v>408704.99829999899</v>
@@ -3674,7 +3674,7 @@
         <v>126</v>
       </c>
       <c r="B83" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C83">
         <v>408698.93699999899</v>
@@ -3691,7 +3691,7 @@
         <v>121</v>
       </c>
       <c r="B84" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C84">
         <v>408704.38349999901</v>
@@ -3708,7 +3708,7 @@
         <v>124</v>
       </c>
       <c r="B85" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C85">
         <v>408698.26829999901</v>
@@ -3735,13 +3735,13 @@
         <v>201</v>
       </c>
       <c r="B1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E1" t="s">
         <v>12</v>
@@ -3752,7 +3752,7 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C2">
         <v>408914.35340000002</v>
@@ -3769,7 +3769,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C3">
         <v>408913.7599</v>
@@ -3786,7 +3786,7 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C4">
         <v>408913.14380000002</v>
@@ -3803,7 +3803,7 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C5">
         <v>408912.52870000002</v>
@@ -3820,7 +3820,7 @@
         <v>153</v>
       </c>
       <c r="B6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C6">
         <v>408900.20380000002</v>
@@ -3837,7 +3837,7 @@
         <v>154</v>
       </c>
       <c r="B7" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C7">
         <v>408899.61949999898</v>
@@ -3854,7 +3854,7 @@
         <v>155</v>
       </c>
       <c r="B8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C8">
         <v>408899.00260000001</v>
@@ -3871,7 +3871,7 @@
         <v>156</v>
       </c>
       <c r="B9" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C9">
         <v>408898.37829999899</v>
@@ -3888,7 +3888,7 @@
         <v>157</v>
       </c>
       <c r="B10" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C10">
         <v>408885.99040000001</v>
@@ -3905,7 +3905,7 @@
         <v>158</v>
       </c>
       <c r="B11" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C11">
         <v>408885.37439999898</v>
@@ -3922,7 +3922,7 @@
         <v>159</v>
       </c>
       <c r="B12" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C12">
         <v>408884.80279999902</v>
@@ -3939,7 +3939,7 @@
         <v>160</v>
       </c>
       <c r="B13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C13">
         <v>408884.17149999901</v>
@@ -3956,7 +3956,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C14">
         <v>408859.25290000002</v>
@@ -3973,7 +3973,7 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C15">
         <v>408858.64659999899</v>
@@ -3990,7 +3990,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C16">
         <v>408858.0344</v>
@@ -4007,7 +4007,7 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C17">
         <v>408857.44079999899</v>
@@ -4024,7 +4024,7 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C18">
         <v>408845.03460000001</v>
@@ -4041,7 +4041,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C19">
         <v>408844.4375</v>
@@ -4058,7 +4058,7 @@
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C20">
         <v>408843.829399999</v>
@@ -4075,7 +4075,7 @@
         <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C21">
         <v>408843.20490000001</v>
@@ -4092,7 +4092,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C22">
         <v>408830.81489999901</v>
@@ -4109,7 +4109,7 @@
         <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C23">
         <v>408830.206899999</v>
@@ -4126,7 +4126,7 @@
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C24">
         <v>408829.59519999899</v>
@@ -4143,7 +4143,7 @@
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C25">
         <v>408828.99920000002</v>
@@ -4160,7 +4160,7 @@
         <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C26">
         <v>408816.59179999901</v>
@@ -4177,7 +4177,7 @@
         <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C27">
         <v>408815.986199999</v>
@@ -4194,7 +4194,7 @@
         <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C28">
         <v>408815.39</v>
@@ -4211,7 +4211,7 @@
         <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C29">
         <v>408814.777</v>
@@ -4228,7 +4228,7 @@
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C30">
         <v>408802.449499999</v>
@@ -4245,7 +4245,7 @@
         <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C31">
         <v>408801.83819999901</v>
@@ -4262,7 +4262,7 @@
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C32">
         <v>408801.21379999898</v>
@@ -4279,7 +4279,7 @@
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C33">
         <v>408800.62819999899</v>
@@ -4296,7 +4296,7 @@
         <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C34">
         <v>408788.22350000002</v>
@@ -4313,7 +4313,7 @@
         <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C35">
         <v>408787.60700000002</v>
@@ -4330,7 +4330,7 @@
         <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C36">
         <v>408787.00040000002</v>
@@ -4347,7 +4347,7 @@
         <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C37">
         <v>408786.40159999899</v>
@@ -4364,7 +4364,7 @@
         <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C38">
         <v>408773.99790000002</v>
@@ -4381,7 +4381,7 @@
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C39">
         <v>408773.39649999898</v>
@@ -4398,7 +4398,7 @@
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C40">
         <v>408772.784099999</v>
@@ -4415,7 +4415,7 @@
         <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C41">
         <v>408772.17050000001</v>
@@ -4432,7 +4432,7 @@
         <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C42">
         <v>408759.7758</v>
@@ -4449,7 +4449,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C43">
         <v>408759.1692</v>
@@ -4466,7 +4466,7 @@
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C44">
         <v>408758.57179999899</v>
@@ -4483,7 +4483,7 @@
         <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C45">
         <v>408757.959299999</v>
@@ -4500,7 +4500,7 @@
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C46">
         <v>408745.63719999901</v>
@@ -4517,7 +4517,7 @@
         <v>50</v>
       </c>
       <c r="B47" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C47">
         <v>408745.02610000002</v>
@@ -4534,7 +4534,7 @@
         <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C48">
         <v>408744.41419999901</v>
@@ -4551,7 +4551,7 @@
         <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C49">
         <v>408743.81449999899</v>
@@ -4568,7 +4568,7 @@
         <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C50">
         <v>408731.41739999899</v>
@@ -4585,7 +4585,7 @@
         <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C51">
         <v>408730.80660000001</v>
@@ -4602,7 +4602,7 @@
         <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C52">
         <v>408730.19</v>
@@ -4619,7 +4619,7 @@
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C53">
         <v>408729.61050000001</v>
@@ -4636,7 +4636,7 @@
         <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C54">
         <v>408717.2047</v>
@@ -4653,7 +4653,7 @@
         <v>58</v>
       </c>
       <c r="B55" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C55">
         <v>408716.59240000002</v>
@@ -4670,7 +4670,7 @@
         <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C56">
         <v>408715.98029999901</v>
@@ -4687,7 +4687,7 @@
         <v>60</v>
       </c>
       <c r="B57" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C57">
         <v>408715.38030000002</v>
@@ -4704,7 +4704,7 @@
         <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C58">
         <v>408702.95299999899</v>
@@ -4721,7 +4721,7 @@
         <v>62</v>
       </c>
       <c r="B59" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C59">
         <v>408702.35950000002</v>
@@ -4738,7 +4738,7 @@
         <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C60">
         <v>408701.76500000001</v>
@@ -4755,7 +4755,7 @@
         <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C61">
         <v>408701.14669999899</v>
@@ -4785,211 +4785,211 @@
         <v>200</v>
       </c>
       <c r="C1" t="s">
+        <v>474</v>
+      </c>
+      <c r="D1" t="s">
         <v>259</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>260</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>261</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>262</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>263</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>264</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>265</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>266</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>267</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>268</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>269</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>270</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>271</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>272</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>273</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>274</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>275</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>276</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>277</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>278</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>279</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>280</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>281</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>282</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>283</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>284</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>285</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>286</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>287</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>288</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>289</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>290</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>291</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>292</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>293</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>294</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>295</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>296</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>297</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>298</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>299</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>300</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>301</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>302</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>303</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>304</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>305</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>306</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>307</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>308</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>309</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>310</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>311</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>312</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>313</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>314</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>315</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>316</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>317</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>318</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>319</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>320</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>321</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>322</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>323</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>324</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>325</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>326</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
@@ -45474,211 +45474,211 @@
         <v>12</v>
       </c>
       <c r="C1" t="s">
+        <v>474</v>
+      </c>
+      <c r="D1" t="s">
         <v>259</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>260</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>261</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>262</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>263</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>264</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>265</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>266</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>267</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>268</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>269</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>270</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>271</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>272</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>273</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>274</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>275</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>276</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>277</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>278</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>279</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>280</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>281</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>282</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>283</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>284</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>285</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>286</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>287</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>288</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>289</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>290</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>291</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>292</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>293</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>294</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>295</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>296</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>297</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>298</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>299</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>300</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>301</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>302</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>303</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>304</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>305</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>306</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>307</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>308</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>309</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>310</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>311</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>312</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>313</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>314</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>315</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>316</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>317</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>318</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>319</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>320</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>321</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>322</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>323</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>324</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>325</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>326</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">

--- a/Data/2018_F013B4_CO_ITR/2018_F013B4_CO_ITR_SoilAnalysis.xlsx
+++ b/Data/2018_F013B4_CO_ITR/2018_F013B4_CO_ITR_SoilAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2018_F013B4_CO_ITR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD63872-5A36-4835-869B-D28242CBA94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7353B68B-D9E4-4F09-B2DC-56B91A1CD5FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1515" yWindow="-24870" windowWidth="17775" windowHeight="24285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1815" yWindow="-27240" windowWidth="16335" windowHeight="23370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDJH" sheetId="5" r:id="rId1"/>
@@ -812,12 +812,6 @@
     <t>p01-1</t>
   </si>
   <si>
-    <t>2015d118EM38</t>
-  </si>
-  <si>
-    <t>2015d119EM38</t>
-  </si>
-  <si>
     <t>SLSND015</t>
   </si>
   <si>
@@ -1458,6 +1452,12 @@
   </si>
   <si>
     <t>2013d260EM38V</t>
+  </si>
+  <si>
+    <t>2015d118EM38V</t>
+  </si>
+  <si>
+    <t>2015d119EM38V</t>
   </si>
 </sst>
 </file>
@@ -2280,13 +2280,13 @@
         <v>201</v>
       </c>
       <c r="B1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E1" t="s">
         <v>12</v>
@@ -2297,7 +2297,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C2">
         <v>408901.33329999901</v>
@@ -2314,7 +2314,7 @@
         <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C3">
         <v>408900.44150000002</v>
@@ -2331,7 +2331,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C4">
         <v>408899.99949999899</v>
@@ -2348,7 +2348,7 @@
         <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C5">
         <v>408899.580599999</v>
@@ -2365,7 +2365,7 @@
         <v>151</v>
       </c>
       <c r="B6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C6">
         <v>408879.86940000003</v>
@@ -2382,7 +2382,7 @@
         <v>152</v>
       </c>
       <c r="B7" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C7">
         <v>408879.400499999</v>
@@ -2399,7 +2399,7 @@
         <v>153</v>
       </c>
       <c r="B8" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C8">
         <v>408878.89939999901</v>
@@ -2416,7 +2416,7 @@
         <v>155</v>
       </c>
       <c r="B9" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C9">
         <v>408877.92340000003</v>
@@ -2433,7 +2433,7 @@
         <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C10">
         <v>408872.89059999899</v>
@@ -2450,7 +2450,7 @@
         <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C11">
         <v>408872.00809999899</v>
@@ -2467,7 +2467,7 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C12">
         <v>408871.57900000003</v>
@@ -2484,7 +2484,7 @@
         <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C13">
         <v>408871.13660000003</v>
@@ -2501,7 +2501,7 @@
         <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C14">
         <v>408845.46089999902</v>
@@ -2518,7 +2518,7 @@
         <v>156</v>
       </c>
       <c r="B15" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C15">
         <v>408850.18070000003</v>
@@ -2535,7 +2535,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C16">
         <v>408844.56319999899</v>
@@ -2552,7 +2552,7 @@
         <v>157</v>
       </c>
       <c r="B17" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C17">
         <v>408849.70020000002</v>
@@ -2569,7 +2569,7 @@
         <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C18">
         <v>408844.13500000001</v>
@@ -2586,7 +2586,7 @@
         <v>158</v>
       </c>
       <c r="B19" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C19">
         <v>408849.219199999</v>
@@ -2603,7 +2603,7 @@
         <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C20">
         <v>408843.68329999998</v>
@@ -2620,7 +2620,7 @@
         <v>160</v>
       </c>
       <c r="B21" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C21">
         <v>408848.231299999</v>
@@ -2637,7 +2637,7 @@
         <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C22">
         <v>408817.00829999999</v>
@@ -2654,7 +2654,7 @@
         <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C23">
         <v>408816.12689999898</v>
@@ -2671,7 +2671,7 @@
         <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C24">
         <v>408815.666399999</v>
@@ -2688,7 +2688,7 @@
         <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C25">
         <v>408815.248499999</v>
@@ -2705,7 +2705,7 @@
         <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C26">
         <v>408788.581799999</v>
@@ -2722,7 +2722,7 @@
         <v>166</v>
       </c>
       <c r="B27" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C27">
         <v>408793.35800000001</v>
@@ -2739,7 +2739,7 @@
         <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C28">
         <v>408787.67560000002</v>
@@ -2756,7 +2756,7 @@
         <v>167</v>
       </c>
       <c r="B29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C29">
         <v>408792.866099999</v>
@@ -2773,7 +2773,7 @@
         <v>52</v>
       </c>
       <c r="B30" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C30">
         <v>408787.222799999</v>
@@ -2790,7 +2790,7 @@
         <v>168</v>
       </c>
       <c r="B31" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C31">
         <v>408792.38530000002</v>
@@ -2807,7 +2807,7 @@
         <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C32">
         <v>408786.80749999901</v>
@@ -2824,7 +2824,7 @@
         <v>170</v>
       </c>
       <c r="B33" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C33">
         <v>408791.43050000002</v>
@@ -2841,7 +2841,7 @@
         <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C34">
         <v>408760.11839999899</v>
@@ -2858,7 +2858,7 @@
         <v>58</v>
       </c>
       <c r="B35" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C35">
         <v>408759.24219999899</v>
@@ -2875,7 +2875,7 @@
         <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C36">
         <v>408758.807399999</v>
@@ -2892,7 +2892,7 @@
         <v>56</v>
       </c>
       <c r="B37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C37">
         <v>408758.367499999</v>
@@ -2909,7 +2909,7 @@
         <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C38">
         <v>408748.9094</v>
@@ -2926,7 +2926,7 @@
         <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C39">
         <v>408748.6594</v>
@@ -2943,7 +2943,7 @@
         <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C40">
         <v>408742.57679999899</v>
@@ -2960,7 +2960,7 @@
         <v>82</v>
       </c>
       <c r="B41" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C41">
         <v>408742.84710000001</v>
@@ -2977,7 +2977,7 @@
         <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C42">
         <v>408748.33390000003</v>
@@ -2994,7 +2994,7 @@
         <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C43">
         <v>408747.98800000001</v>
@@ -3011,7 +3011,7 @@
         <v>79</v>
       </c>
       <c r="B44" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C44">
         <v>408741.9215</v>
@@ -3028,7 +3028,7 @@
         <v>80</v>
       </c>
       <c r="B45" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C45">
         <v>408742.204399999</v>
@@ -3045,7 +3045,7 @@
         <v>71</v>
       </c>
       <c r="B46" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C46">
         <v>408747.652899999</v>
@@ -3062,7 +3062,7 @@
         <v>78</v>
       </c>
       <c r="B47" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C47">
         <v>408741.583099999</v>
@@ -3079,7 +3079,7 @@
         <v>73</v>
       </c>
       <c r="B48" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C48">
         <v>408747.01990000001</v>
@@ -3096,7 +3096,7 @@
         <v>76</v>
       </c>
       <c r="B49" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C49">
         <v>408740.96580000001</v>
@@ -3113,7 +3113,7 @@
         <v>83</v>
       </c>
       <c r="B50" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C50">
         <v>408734.69020000001</v>
@@ -3130,7 +3130,7 @@
         <v>84</v>
       </c>
       <c r="B51" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C51">
         <v>408734.44760000001</v>
@@ -3147,7 +3147,7 @@
         <v>97</v>
       </c>
       <c r="B52" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C52">
         <v>408728.347899999</v>
@@ -3164,7 +3164,7 @@
         <v>98</v>
       </c>
       <c r="B53" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C53">
         <v>408728.57990000001</v>
@@ -3181,7 +3181,7 @@
         <v>85</v>
       </c>
       <c r="B54" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C54">
         <v>408734.16200000001</v>
@@ -3198,7 +3198,7 @@
         <v>86</v>
       </c>
       <c r="B55" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C55">
         <v>408733.81439999898</v>
@@ -3215,7 +3215,7 @@
         <v>95</v>
       </c>
       <c r="B56" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C56">
         <v>408727.74089999998</v>
@@ -3232,7 +3232,7 @@
         <v>96</v>
       </c>
       <c r="B57" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C57">
         <v>408727.98920000001</v>
@@ -3249,7 +3249,7 @@
         <v>87</v>
       </c>
       <c r="B58" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C58">
         <v>408733.443499999</v>
@@ -3266,7 +3266,7 @@
         <v>94</v>
       </c>
       <c r="B59" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C59">
         <v>408727.3763</v>
@@ -3283,7 +3283,7 @@
         <v>89</v>
       </c>
       <c r="B60" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C60">
         <v>408732.84250000003</v>
@@ -3300,7 +3300,7 @@
         <v>92</v>
       </c>
       <c r="B61" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C61">
         <v>408726.75140000001</v>
@@ -3317,7 +3317,7 @@
         <v>99</v>
       </c>
       <c r="B62" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C62">
         <v>408720.46580000001</v>
@@ -3334,7 +3334,7 @@
         <v>100</v>
       </c>
       <c r="B63" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C63">
         <v>408720.19679999899</v>
@@ -3351,7 +3351,7 @@
         <v>113</v>
       </c>
       <c r="B64" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C64">
         <v>408714.09700000001</v>
@@ -3368,7 +3368,7 @@
         <v>114</v>
       </c>
       <c r="B65" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C65">
         <v>408714.40309999901</v>
@@ -3385,7 +3385,7 @@
         <v>101</v>
       </c>
       <c r="B66" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C66">
         <v>408719.8885</v>
@@ -3402,7 +3402,7 @@
         <v>102</v>
       </c>
       <c r="B67" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C67">
         <v>408719.60830000002</v>
@@ -3419,7 +3419,7 @@
         <v>111</v>
       </c>
       <c r="B68" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C68">
         <v>408713.53340000001</v>
@@ -3436,7 +3436,7 @@
         <v>112</v>
       </c>
       <c r="B69" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C69">
         <v>408713.790299999</v>
@@ -3453,7 +3453,7 @@
         <v>103</v>
       </c>
       <c r="B70" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C70">
         <v>408719.22999999899</v>
@@ -3470,7 +3470,7 @@
         <v>110</v>
       </c>
       <c r="B71" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C71">
         <v>408713.13880000002</v>
@@ -3487,7 +3487,7 @@
         <v>105</v>
       </c>
       <c r="B72" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C72">
         <v>408718.61729999899</v>
@@ -3504,7 +3504,7 @@
         <v>108</v>
       </c>
       <c r="B73" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C73">
         <v>408712.455599999</v>
@@ -3521,7 +3521,7 @@
         <v>115</v>
       </c>
       <c r="B74" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C74">
         <v>408706.2476</v>
@@ -3538,7 +3538,7 @@
         <v>116</v>
       </c>
       <c r="B75" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C75">
         <v>408705.94109999901</v>
@@ -3555,7 +3555,7 @@
         <v>129</v>
       </c>
       <c r="B76" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C76">
         <v>408699.85230000003</v>
@@ -3572,7 +3572,7 @@
         <v>130</v>
       </c>
       <c r="B77" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C77">
         <v>408700.13030000002</v>
@@ -3589,7 +3589,7 @@
         <v>117</v>
       </c>
       <c r="B78" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C78">
         <v>408705.62539999897</v>
@@ -3606,7 +3606,7 @@
         <v>118</v>
       </c>
       <c r="B79" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C79">
         <v>408705.38500000001</v>
@@ -3623,7 +3623,7 @@
         <v>127</v>
       </c>
       <c r="B80" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C80">
         <v>408699.26530000003</v>
@@ -3640,7 +3640,7 @@
         <v>128</v>
       </c>
       <c r="B81" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C81">
         <v>408699.535299999</v>
@@ -3657,7 +3657,7 @@
         <v>119</v>
       </c>
       <c r="B82" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C82">
         <v>408704.99829999899</v>
@@ -3674,7 +3674,7 @@
         <v>126</v>
       </c>
       <c r="B83" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C83">
         <v>408698.93699999899</v>
@@ -3691,7 +3691,7 @@
         <v>121</v>
       </c>
       <c r="B84" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C84">
         <v>408704.38349999901</v>
@@ -3708,7 +3708,7 @@
         <v>124</v>
       </c>
       <c r="B85" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C85">
         <v>408698.26829999901</v>
@@ -3735,13 +3735,13 @@
         <v>201</v>
       </c>
       <c r="B1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E1" t="s">
         <v>12</v>
@@ -3752,7 +3752,7 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C2">
         <v>408914.35340000002</v>
@@ -3769,7 +3769,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C3">
         <v>408913.7599</v>
@@ -3786,7 +3786,7 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C4">
         <v>408913.14380000002</v>
@@ -3803,7 +3803,7 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C5">
         <v>408912.52870000002</v>
@@ -3820,7 +3820,7 @@
         <v>153</v>
       </c>
       <c r="B6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C6">
         <v>408900.20380000002</v>
@@ -3837,7 +3837,7 @@
         <v>154</v>
       </c>
       <c r="B7" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C7">
         <v>408899.61949999898</v>
@@ -3854,7 +3854,7 @@
         <v>155</v>
       </c>
       <c r="B8" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C8">
         <v>408899.00260000001</v>
@@ -3871,7 +3871,7 @@
         <v>156</v>
       </c>
       <c r="B9" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C9">
         <v>408898.37829999899</v>
@@ -3888,7 +3888,7 @@
         <v>157</v>
       </c>
       <c r="B10" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C10">
         <v>408885.99040000001</v>
@@ -3905,7 +3905,7 @@
         <v>158</v>
       </c>
       <c r="B11" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C11">
         <v>408885.37439999898</v>
@@ -3922,7 +3922,7 @@
         <v>159</v>
       </c>
       <c r="B12" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C12">
         <v>408884.80279999902</v>
@@ -3939,7 +3939,7 @@
         <v>160</v>
       </c>
       <c r="B13" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C13">
         <v>408884.17149999901</v>
@@ -3956,7 +3956,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C14">
         <v>408859.25290000002</v>
@@ -3973,7 +3973,7 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C15">
         <v>408858.64659999899</v>
@@ -3990,7 +3990,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C16">
         <v>408858.0344</v>
@@ -4007,7 +4007,7 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C17">
         <v>408857.44079999899</v>
@@ -4024,7 +4024,7 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C18">
         <v>408845.03460000001</v>
@@ -4041,7 +4041,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C19">
         <v>408844.4375</v>
@@ -4058,7 +4058,7 @@
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C20">
         <v>408843.829399999</v>
@@ -4075,7 +4075,7 @@
         <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C21">
         <v>408843.20490000001</v>
@@ -4092,7 +4092,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C22">
         <v>408830.81489999901</v>
@@ -4109,7 +4109,7 @@
         <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C23">
         <v>408830.206899999</v>
@@ -4126,7 +4126,7 @@
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C24">
         <v>408829.59519999899</v>
@@ -4143,7 +4143,7 @@
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C25">
         <v>408828.99920000002</v>
@@ -4160,7 +4160,7 @@
         <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C26">
         <v>408816.59179999901</v>
@@ -4177,7 +4177,7 @@
         <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C27">
         <v>408815.986199999</v>
@@ -4194,7 +4194,7 @@
         <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C28">
         <v>408815.39</v>
@@ -4211,7 +4211,7 @@
         <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C29">
         <v>408814.777</v>
@@ -4228,7 +4228,7 @@
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C30">
         <v>408802.449499999</v>
@@ -4245,7 +4245,7 @@
         <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C31">
         <v>408801.83819999901</v>
@@ -4262,7 +4262,7 @@
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C32">
         <v>408801.21379999898</v>
@@ -4279,7 +4279,7 @@
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C33">
         <v>408800.62819999899</v>
@@ -4296,7 +4296,7 @@
         <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C34">
         <v>408788.22350000002</v>
@@ -4313,7 +4313,7 @@
         <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C35">
         <v>408787.60700000002</v>
@@ -4330,7 +4330,7 @@
         <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C36">
         <v>408787.00040000002</v>
@@ -4347,7 +4347,7 @@
         <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C37">
         <v>408786.40159999899</v>
@@ -4364,7 +4364,7 @@
         <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C38">
         <v>408773.99790000002</v>
@@ -4381,7 +4381,7 @@
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C39">
         <v>408773.39649999898</v>
@@ -4398,7 +4398,7 @@
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C40">
         <v>408772.784099999</v>
@@ -4415,7 +4415,7 @@
         <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C41">
         <v>408772.17050000001</v>
@@ -4432,7 +4432,7 @@
         <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C42">
         <v>408759.7758</v>
@@ -4449,7 +4449,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C43">
         <v>408759.1692</v>
@@ -4466,7 +4466,7 @@
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C44">
         <v>408758.57179999899</v>
@@ -4483,7 +4483,7 @@
         <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C45">
         <v>408757.959299999</v>
@@ -4500,7 +4500,7 @@
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C46">
         <v>408745.63719999901</v>
@@ -4517,7 +4517,7 @@
         <v>50</v>
       </c>
       <c r="B47" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C47">
         <v>408745.02610000002</v>
@@ -4534,7 +4534,7 @@
         <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C48">
         <v>408744.41419999901</v>
@@ -4551,7 +4551,7 @@
         <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C49">
         <v>408743.81449999899</v>
@@ -4568,7 +4568,7 @@
         <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C50">
         <v>408731.41739999899</v>
@@ -4585,7 +4585,7 @@
         <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C51">
         <v>408730.80660000001</v>
@@ -4602,7 +4602,7 @@
         <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C52">
         <v>408730.19</v>
@@ -4619,7 +4619,7 @@
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C53">
         <v>408729.61050000001</v>
@@ -4636,7 +4636,7 @@
         <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C54">
         <v>408717.2047</v>
@@ -4653,7 +4653,7 @@
         <v>58</v>
       </c>
       <c r="B55" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C55">
         <v>408716.59240000002</v>
@@ -4670,7 +4670,7 @@
         <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C56">
         <v>408715.98029999901</v>
@@ -4687,7 +4687,7 @@
         <v>60</v>
       </c>
       <c r="B57" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C57">
         <v>408715.38030000002</v>
@@ -4704,7 +4704,7 @@
         <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C58">
         <v>408702.95299999899</v>
@@ -4721,7 +4721,7 @@
         <v>62</v>
       </c>
       <c r="B59" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C59">
         <v>408702.35950000002</v>
@@ -4738,7 +4738,7 @@
         <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C60">
         <v>408701.76500000001</v>
@@ -4755,7 +4755,7 @@
         <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C61">
         <v>408701.14669999899</v>
@@ -4785,211 +4785,211 @@
         <v>200</v>
       </c>
       <c r="C1" t="s">
+        <v>472</v>
+      </c>
+      <c r="D1" t="s">
+        <v>473</v>
+      </c>
+      <c r="E1" t="s">
         <v>474</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>259</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>260</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>261</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>262</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>263</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>264</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>265</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>266</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>267</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>268</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>269</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>270</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>271</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>272</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>273</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>274</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>275</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>276</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>277</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>278</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>279</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>280</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>281</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>282</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>283</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>284</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>285</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>286</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>287</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>288</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>289</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>290</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>291</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>292</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>293</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>294</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>295</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>296</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>297</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>298</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>299</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>300</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>301</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>302</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>303</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>304</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>305</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>306</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>307</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>308</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>309</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>310</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>311</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>312</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>313</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>314</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>315</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BK1" t="s">
         <v>316</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>317</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>318</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>319</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>320</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>321</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>322</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>323</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>324</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>325</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
@@ -45474,211 +45474,211 @@
         <v>12</v>
       </c>
       <c r="C1" t="s">
+        <v>472</v>
+      </c>
+      <c r="D1" t="s">
+        <v>473</v>
+      </c>
+      <c r="E1" t="s">
         <v>474</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>259</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>260</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>261</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>262</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>263</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>264</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>265</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>266</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>267</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>268</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>269</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>270</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>271</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>272</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>273</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>274</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>275</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>276</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>277</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>278</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>279</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>280</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>281</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>282</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>283</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>284</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>285</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>286</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>287</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>288</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>289</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>290</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>291</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>292</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>293</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>294</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>295</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>296</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>297</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>298</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>299</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>300</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>301</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>302</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>303</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>304</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>305</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>306</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>307</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>308</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>309</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>310</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>311</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>312</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>313</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>314</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>315</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BK1" t="s">
         <v>316</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>317</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>318</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>319</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>320</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>321</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>322</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>323</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>324</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>325</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
